--- a/public/MAU_IMPORT_CHAM_CONG.xlsx
+++ b/public/MAU_IMPORT_CHAM_CONG.xlsx
@@ -1,33 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8BA881-C140-4D30-80AE-DC21AE4D154D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Lớp chung" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Lớp phụ đạo" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Lớp kèm" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Lớp phụ đạo kèm" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Văn phòng" state="visible" r:id="rId8"/>
+    <sheet name="Lớp chung" sheetId="1" r:id="rId1"/>
+    <sheet name="Lớp phụ đạo" sheetId="2" r:id="rId2"/>
+    <sheet name="Lớp kèm" sheetId="3" r:id="rId3"/>
+    <sheet name="Lớp phụ đạo kèm" sheetId="4" r:id="rId4"/>
+    <sheet name="Văn phòng" sheetId="5" r:id="rId5"/>
+    <sheet name="Placement Test" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Ngày
 </t>
@@ -36,20 +42,22 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
-          </rPr>
-          <t xml:space="preserve">• Ngày làm việc.
+            <family val="1"/>
+          </rPr>
+          <t>• Ngày làm việc.
 • Có thể nhập ngày Excel hoặc dd/mm/yyyy.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Thứ
 </t>
@@ -58,19 +66,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Thứ tương ứng với ngày.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên lớp
 </t>
@@ -79,19 +89,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên lớp; giữ nguyên ký hiệu %/ONL nếu có vì dùng để tính lương.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Giờ bắt đầu
 </t>
@@ -100,19 +112,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Giờ bắt đầu.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Giờ kết thúc
 </t>
@@ -121,19 +135,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Giờ kết thúc.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tổng giờ
 </t>
@@ -142,19 +158,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tổng giờ; nếu để trống web có thể tự tính từ giờ bắt đầu/kết thúc.</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên GV
 </t>
@@ -163,19 +181,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên giáo viên.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên TG
 </t>
@@ -184,6 +204,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên trợ giảng.</t>
         </r>
@@ -194,19 +215,20 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Ngày
 </t>
@@ -215,20 +237,22 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
-          </rPr>
-          <t xml:space="preserve">• Ngày làm việc.
+            <family val="1"/>
+          </rPr>
+          <t>• Ngày làm việc.
 • Có thể nhập ngày Excel hoặc dd/mm/yyyy.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Thứ
 </t>
@@ -237,19 +261,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Thứ tương ứng với ngày.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên lớp
 </t>
@@ -258,19 +284,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên lớp; giữ nguyên ký hiệu %/ONL nếu có vì dùng để tính lương.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Giờ bắt đầu
 </t>
@@ -279,19 +307,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Giờ bắt đầu.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Giờ kết thúc
 </t>
@@ -300,19 +330,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Giờ kết thúc.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tổng giờ
 </t>
@@ -321,19 +353,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tổng giờ; nếu để trống web có thể tự tính từ giờ bắt đầu/kết thúc.</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên GV
 </t>
@@ -342,19 +376,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên giáo viên.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên TG
 </t>
@@ -363,6 +399,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên trợ giảng.</t>
         </r>
@@ -373,19 +410,20 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Ngày
 </t>
@@ -394,20 +432,22 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
-          </rPr>
-          <t xml:space="preserve">• Ngày làm việc.
+            <family val="1"/>
+          </rPr>
+          <t>• Ngày làm việc.
 • Có thể nhập ngày Excel hoặc dd/mm/yyyy.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Thứ
 </t>
@@ -416,19 +456,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Thứ tương ứng với ngày.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên lớp
 </t>
@@ -437,19 +479,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên lớp; giữ nguyên ký hiệu %/ONL nếu có vì dùng để tính lương.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Giờ bắt đầu
 </t>
@@ -458,19 +502,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Giờ bắt đầu.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Giờ kết thúc
 </t>
@@ -479,19 +525,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Giờ kết thúc.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tổng giờ
 </t>
@@ -500,19 +548,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tổng giờ; nếu để trống web có thể tự tính từ giờ bắt đầu/kết thúc.</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên GV
 </t>
@@ -521,19 +571,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên giáo viên.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên TG
 </t>
@@ -542,6 +594,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên trợ giảng.</t>
         </r>
@@ -552,19 +605,20 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Ngày
 </t>
@@ -573,20 +627,22 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
-          </rPr>
-          <t xml:space="preserve">• Ngày làm việc.
+            <family val="1"/>
+          </rPr>
+          <t>• Ngày làm việc.
 • Có thể nhập ngày Excel hoặc dd/mm/yyyy.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Thứ
 </t>
@@ -595,19 +651,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Thứ tương ứng với ngày.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên lớp
 </t>
@@ -616,19 +674,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên lớp; giữ nguyên ký hiệu %/ONL nếu có vì dùng để tính lương.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Giờ bắt đầu
 </t>
@@ -637,19 +697,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Giờ bắt đầu.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Giờ kết thúc
 </t>
@@ -658,19 +720,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Giờ kết thúc.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tổng giờ
 </t>
@@ -679,19 +743,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tổng giờ; nếu để trống web có thể tự tính từ giờ bắt đầu/kết thúc.</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên GV
 </t>
@@ -700,19 +766,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên giáo viên.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên TG
 </t>
@@ -721,6 +789,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên trợ giảng.</t>
         </r>
@@ -731,19 +800,20 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Ngày
 </t>
@@ -752,19 +822,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Ngày làm việc.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Thứ
 </t>
@@ -773,19 +845,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Thứ tương ứng với ngày.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tên nhân viên
 </t>
@@ -794,19 +868,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tên nhân viên.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Giờ in
 </t>
@@ -815,19 +891,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Giờ vào.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Giờ out
 </t>
@@ -836,19 +914,21 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Giờ ra.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
+            <sz val="11"/>
             <color rgb="FF064E3B"/>
-            <sz val="11"/>
-            <rFont val="Times New Roman"/>
+            <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t xml:space="preserve">Tổng số giờ
 </t>
@@ -857,6 +937,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Times New Roman"/>
+            <family val="1"/>
           </rPr>
           <t>• Tổng số giờ làm việc.</t>
         </r>
@@ -867,7 +948,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Ngày</t>
   </si>
@@ -893,25 +974,7 @@
     <t>Tên TG</t>
   </si>
   <si>
-    <t>2026-10-01</t>
-  </si>
-  <si>
-    <t>THU 5</t>
-  </si>
-  <si>
     <t>KET 1-6</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn A</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Tên nhân viên</t>
@@ -926,43 +989,106 @@
     <t>Tổng số giờ</t>
   </si>
   <si>
-    <t>08:00</t>
+    <t>THU 3</t>
   </si>
   <si>
-    <t>17:00</t>
+    <t>MOVERS EXAM 3</t>
+  </si>
+  <si>
+    <t>Phạm Thị Anh Đào</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Phương Loan</t>
+  </si>
+  <si>
+    <t>THU 7</t>
+  </si>
+  <si>
+    <t>PET 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KET + FLYERS </t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Trúc</t>
+  </si>
+  <si>
+    <t>NGÀY</t>
+  </si>
+  <si>
+    <t>TÊN HV</t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>BÙI HỮU KHOA</t>
+  </si>
+  <si>
+    <t>STARTERS</t>
+  </si>
+  <si>
+    <t>LÊ THỊ NGUYỆT QUẾ</t>
+  </si>
+  <si>
+    <t>PLACEMENT TEST</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="hh:mm"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF064E3B"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -970,19 +1096,1144 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="53">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -996,8 +2247,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="ClassCommon" displayName="ClassCommon" ref="A1:H2" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:H2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ClassCommon" displayName="ClassCommon" ref="A1:H3" dataDxfId="52">
+  <autoFilter ref="A1:H3" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1008,22 +2259,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" name="Ngày" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Thứ" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Tên lớp" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Giờ bắt đầu" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Giờ kết thúc" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Tổng giờ" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Tên GV" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Tên TG" totalsRowFunction="none"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Ngày" totalsRowLabel="Total" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Thứ" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tên lớp" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Giờ bắt đầu" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Giờ kết thúc" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Tổng giờ" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Tên GV" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Tên TG" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" name="ClassAssist" displayName="ClassAssist" ref="A1:H2" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:H2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ClassAssist" displayName="ClassAssist" ref="A1:H3" dataDxfId="43">
+  <autoFilter ref="A1:H3" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1034,22 +2285,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" name="Ngày" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Thứ" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Tên lớp" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Giờ bắt đầu" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Giờ kết thúc" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Tổng giờ" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Tên GV" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Tên TG" totalsRowFunction="none"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Ngày" totalsRowLabel="Total" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Thứ" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Tên lớp" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Giờ bắt đầu" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Giờ kết thúc" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Tổng giờ" dataDxfId="37"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Tên GV" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Tên TG" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" name="ClassTutoring" displayName="ClassTutoring" ref="A1:H2" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:H2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ClassTutoring" displayName="ClassTutoring" ref="A1:H3" dataDxfId="34">
+  <autoFilter ref="A1:H3" xr:uid="{00000000-0009-0000-0100-000003000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1060,22 +2311,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" name="Ngày" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Thứ" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Tên lớp" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Giờ bắt đầu" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Giờ kết thúc" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Tổng giờ" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Tên GV" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Tên TG" totalsRowFunction="none"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Ngày" totalsRowLabel="Total" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Thứ" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Tên lớp" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Giờ bắt đầu" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Giờ kết thúc" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Tổng giờ" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Tên GV" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Tên TG" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" name="ClassAssistTutoring" displayName="ClassAssistTutoring" ref="A1:H2" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:H2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ClassAssistTutoring" displayName="ClassAssistTutoring" ref="A1:H3" dataDxfId="25">
+  <autoFilter ref="A1:H3" xr:uid="{00000000-0009-0000-0100-000004000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1086,22 +2337,22 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" name="Ngày" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Thứ" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Tên lớp" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Giờ bắt đầu" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Giờ kết thúc" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Tổng giờ" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Tên GV" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Tên TG" totalsRowFunction="none"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Ngày" totalsRowLabel="Total" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Thứ" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Tên lớp" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Giờ bắt đầu" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Giờ kết thúc" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Tổng giờ" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Tên GV" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Tên TG" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" name="Office" displayName="Office" ref="A1:F2" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:F2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Office" displayName="Office" ref="A1:F3" dataDxfId="16">
+  <autoFilter ref="A1:F3" xr:uid="{00000000-0009-0000-0100-000005000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1110,12 +2361,26 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" name="Ngày" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Thứ" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Tên nhân viên" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Giờ in" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Giờ out" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Tổng số giờ" totalsRowFunction="none"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Ngày" totalsRowLabel="Total" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Thứ" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Tên nhân viên" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Giờ in" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Giờ out" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Tổng số giờ" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{CA7F1563-0AB9-4E17-9D7C-27CDC701556E}" name="Table6" displayName="Table6" ref="A1:E3" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+  <autoFilter ref="A1:E3" xr:uid="{CA7F1563-0AB9-4E17-9D7C-27CDC701556E}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{2299317B-217E-4B1A-A7AD-80AC20B4C545}" name="NGÀY" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{7237B1AF-CFC5-437E-AAA6-53E024024B51}" name="Thứ" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{1B2066D5-7CD1-4BD1-8C66-7786A9CB65A3}" name="TÊN HV" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{9F5E6454-FACC-409F-9D95-E61FFA588D95}" name="PLACEMENT TEST" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{2FF4781D-C400-40C5-83DB-BD8000BF0B13}" name="Tên GV" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1442,14 +2707,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H104"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="8" width="18" customWidth="1"/>
+    <col min="1" max="2" width="12.7265625" customWidth="1"/>
+    <col min="3" max="3" width="29.36328125" customWidth="1"/>
+    <col min="4" max="6" width="12.7265625" customWidth="1"/>
+    <col min="7" max="8" width="34.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1475,51 +2743,1084 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.8125</v>
+      </c>
+      <c r="F2" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="D3" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.8125</v>
+      </c>
+      <c r="F3" s="6">
         <v>1.5</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="3"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="3"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="3"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="3"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="3"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="3"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="3"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="3"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" s="3"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="3"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47" s="3"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="3"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49" s="3"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" s="3"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A51" s="3"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A52" s="3"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A53" s="3"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A54" s="3"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A55" s="3"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A56" s="3"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A57" s="3"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A58" s="3"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A59" s="3"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A61" s="3"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A62" s="3"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A63" s="3"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A64" s="3"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A65" s="3"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A66" s="3"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A67" s="3"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A68" s="3"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A69" s="3"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A70" s="3"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A71" s="3"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A72" s="3"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A73" s="3"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A74" s="3"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A75" s="3"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A76" s="3"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A77" s="3"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A78" s="3"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A79" s="3"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A80" s="3"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" s="3"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" s="3"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83" s="3"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" s="3"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="3"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" s="3"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" s="3"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" s="3"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89" s="3"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90" s="3"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" s="3"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" s="3"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="3"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" s="3"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="3"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" s="3"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A97" s="3"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A98" s="3"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A99" s="3"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A100" s="3"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A101" s="3"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A102" s="3"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A103" s="3"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A104" s="3"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="8" width="18" customWidth="1"/>
+    <col min="1" max="6" width="15.36328125" customWidth="1"/>
+    <col min="7" max="8" width="23.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1545,51 +3846,443 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G2" s="2" t="s">
+    <row r="2" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="C2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0.8125</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.50000000000000089</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.8125</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.50000000000000089</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="3"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="3"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="3"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="3"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1615,51 +4308,35 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
-      </c>
+    <row r="2" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1685,51 +4362,37 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
-      </c>
+    <row r="2" spans="1:8" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:F107"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="6" width="18" customWidth="1"/>
+    <col min="1" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="38.26953125" customWidth="1"/>
+    <col min="4" max="6" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1737,44 +4400,950 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2.4999999999999991</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2">
-        <v>8</v>
-      </c>
+      <c r="D3" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="F3" s="6">
+        <v>6.9999999999999991</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="3"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="3"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="3"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="3"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="3"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="3"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="3"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="3"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="3"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="3"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="3"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="3"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="3"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="3"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="3"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="6"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="3"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="6"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="3"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="6"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="3"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="6"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="3"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="6"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="3"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="6"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="3"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="6"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="3"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="6"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="3"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="6"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="3"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="6"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="6"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="3"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="6"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="3"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="6"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="3"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="6"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="3"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="6"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="3"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="6"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="3"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="6"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="3"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="6"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="3"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="6"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="3"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="6"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="3"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="6"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="3"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="6"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="3"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="6"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="3"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="6"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="3"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="6"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="3"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="6"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="3"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="6"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="3"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="6"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="3"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="6"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="3"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="6"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="3"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="6"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="3"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="6"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="3"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="6"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="3"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="6"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="3"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="6"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="3"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="6"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="3"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="6"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="3"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="6"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="3"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="6"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="3"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="6"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="3"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="6"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="3"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="6"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="3"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="6"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="3"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="6"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="3"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="6"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="3"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="6"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="3"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="6"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="3"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="6"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="3"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="6"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="3"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="6"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="3"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="6"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="3"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="6"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="3"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="6"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="3"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="6"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="3"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="6"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="3"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="6"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="3"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="6"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="3"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="5"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D535DF-87BF-4A39-96A3-638387905D22}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.81640625" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" customWidth="1"/>
+    <col min="3" max="3" width="27.6328125" customWidth="1"/>
+    <col min="4" max="4" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>